--- a/data/stx_xlsx/PROFb.ST.xlsx
+++ b/data/stx_xlsx/PROFb.ST.xlsx
@@ -9215,14 +9215,38 @@
       <c r="O20" s="18">
         <v>90.74</v>
       </c>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
+      <c r="P20" s="18">
+        <f t="shared" ref="P20:W20" si="1">SUM(P21:P23)</f>
+        <v>100.3</v>
+      </c>
+      <c r="Q20" s="18">
+        <f t="shared" si="1"/>
+        <v>87.29</v>
+      </c>
+      <c r="R20" s="18">
+        <f t="shared" si="1"/>
+        <v>67.96</v>
+      </c>
+      <c r="S20" s="18">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="T20" s="18">
+        <f t="shared" si="1"/>
+        <v>112.19</v>
+      </c>
+      <c r="U20" s="18">
+        <f t="shared" si="1"/>
+        <v>92.52</v>
+      </c>
+      <c r="V20" s="18">
+        <f t="shared" si="1"/>
+        <v>71.67</v>
+      </c>
+      <c r="W20" s="18">
+        <f t="shared" si="1"/>
+        <v>79.1</v>
+      </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
@@ -10320,35 +10344,35 @@
         <v>187.21</v>
       </c>
       <c r="P40" s="19">
-        <f t="shared" ref="P40:W40" si="1">P39+P41+P44</f>
+        <f t="shared" ref="P40:W40" si="2">P39+P41+P44</f>
         <v>212.59</v>
       </c>
       <c r="Q40" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>218.91</v>
       </c>
       <c r="R40" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>226.47</v>
       </c>
       <c r="S40" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>252.72</v>
       </c>
       <c r="T40" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>215.3</v>
       </c>
       <c r="U40" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>249.4</v>
       </c>
       <c r="V40" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>248.46</v>
       </c>
       <c r="W40" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>268.08</v>
       </c>
     </row>
